--- a/research/traditional_assets/database/data/israel/israel_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_brokerage_investment_banking.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ6"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.155</v>
+        <v>0.0307</v>
       </c>
       <c r="E2">
-        <v>0.311</v>
+        <v>0.0733</v>
       </c>
       <c r="G2">
-        <v>0.2303117309269893</v>
+        <v>0.3328735632183908</v>
       </c>
       <c r="H2">
-        <v>0.1728876127973749</v>
+        <v>0.3328735632183908</v>
       </c>
       <c r="I2">
-        <v>0.2186218211648892</v>
+        <v>0.2197701149425287</v>
       </c>
       <c r="J2">
-        <v>0.1934281779166628</v>
+        <v>0.1771868571465101</v>
       </c>
       <c r="K2">
-        <v>73.90000000000001</v>
+        <v>52.68</v>
       </c>
       <c r="L2">
-        <v>0.3031173092698934</v>
+        <v>0.2422068965517241</v>
       </c>
       <c r="M2">
-        <v>69.09999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="N2">
-        <v>0.04775067376131573</v>
+        <v>0.09687246141348498</v>
       </c>
       <c r="O2">
-        <v>0.9350473612990526</v>
+        <v>0.9054669703872438</v>
       </c>
       <c r="P2">
-        <v>69.09999999999999</v>
+        <v>47.7</v>
       </c>
       <c r="Q2">
-        <v>0.04775067376131573</v>
+        <v>0.09687246141348498</v>
       </c>
       <c r="R2">
-        <v>0.9350473612990526</v>
+        <v>0.9054669703872438</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>67.848</v>
+        <v>54.993</v>
       </c>
       <c r="V2">
-        <v>0.04688549512818741</v>
+        <v>0.1116835905767669</v>
       </c>
       <c r="W2">
-        <v>0.3409632079371641</v>
+        <v>0.1708333333333333</v>
       </c>
       <c r="X2">
-        <v>0.03656896551176231</v>
+        <v>0.07191083334417672</v>
       </c>
       <c r="Y2">
-        <v>0.3043942424254018</v>
+        <v>0.09892249998915659</v>
       </c>
       <c r="Z2">
-        <v>0.7950924727115001</v>
+        <v>0.8247946545722065</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03645190958779426</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="AC2">
-        <v>-0.03644308868355802</v>
+        <v>-0.07134623617821302</v>
       </c>
       <c r="AD2">
-        <v>47.41999999999999</v>
+        <v>46.562</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>47.41999999999999</v>
+        <v>46.562</v>
       </c>
       <c r="AG2">
-        <v>-20.428</v>
+        <v>-8.430999999999997</v>
       </c>
       <c r="AH2">
-        <v>0.03172925086315338</v>
+        <v>0.0863919905299446</v>
       </c>
       <c r="AI2">
-        <v>0.1226844665217841</v>
+        <v>0.1429764602563394</v>
       </c>
       <c r="AJ2">
-        <v>-0.01431863806116613</v>
+        <v>-0.01742053726581661</v>
       </c>
       <c r="AK2">
-        <v>-0.06410352964803938</v>
+        <v>-0.0311487462546505</v>
       </c>
       <c r="AL2">
-        <v>0.007</v>
+        <v>1.37</v>
       </c>
       <c r="AM2">
-        <v>-2.261</v>
+        <v>0.9720000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.8261324041811845</v>
+        <v>0.8937044145873321</v>
       </c>
       <c r="AO2">
-        <v>7614.285714285714</v>
+        <v>34.8905109489051</v>
       </c>
       <c r="AP2">
-        <v>-0.3558885017421603</v>
+        <v>-0.1618234165067178</v>
       </c>
       <c r="AQ2">
-        <v>-23.57363998230871</v>
+        <v>49.17695473251028</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.155</v>
+        <v>0.161</v>
       </c>
       <c r="E3">
-        <v>0.363</v>
+        <v>0.115</v>
       </c>
       <c r="G3">
-        <v>0.2791358726549176</v>
+        <v>0.4182553437319469</v>
       </c>
       <c r="H3">
-        <v>0.2791358726549176</v>
+        <v>0.4182553437319469</v>
       </c>
       <c r="I3">
-        <v>0.3871517907902217</v>
+        <v>0.2761409589832467</v>
       </c>
       <c r="J3">
-        <v>0.3158343556446545</v>
+        <v>0.1826589416882501</v>
       </c>
       <c r="K3">
-        <v>47.7</v>
+        <v>21.3</v>
       </c>
       <c r="L3">
-        <v>0.2711768050028425</v>
+        <v>0.123050259965338</v>
       </c>
       <c r="M3">
-        <v>26</v>
+        <v>10.2</v>
       </c>
       <c r="N3">
-        <v>0.06498375406148463</v>
+        <v>0.04028436018957346</v>
       </c>
       <c r="O3">
-        <v>0.5450733752620545</v>
+        <v>0.4788732394366197</v>
       </c>
       <c r="P3">
-        <v>26</v>
+        <v>10.2</v>
       </c>
       <c r="Q3">
-        <v>0.06498375406148463</v>
+        <v>0.04028436018957346</v>
       </c>
       <c r="R3">
-        <v>0.5450733752620545</v>
+        <v>0.4788732394366197</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,70 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>27.8</v>
+        <v>31.3</v>
       </c>
       <c r="V3">
-        <v>0.06948262934266433</v>
+        <v>0.1236176935229068</v>
       </c>
       <c r="W3">
-        <v>0.3233898305084746</v>
+        <v>0.1219931271477663</v>
       </c>
       <c r="X3">
-        <v>0.03824237504083707</v>
+        <v>0.07585951992501166</v>
       </c>
       <c r="Y3">
-        <v>0.2851474554676375</v>
+        <v>0.04613360722275467</v>
       </c>
       <c r="Z3">
-        <v>0.9128178515827711</v>
+        <v>0.9058084772370488</v>
       </c>
       <c r="AA3">
-        <v>0.2882992379755824</v>
+        <v>0.1654540178243646</v>
       </c>
       <c r="AB3">
-        <v>0.03668174893832626</v>
+        <v>0.07085471835066295</v>
       </c>
       <c r="AC3">
-        <v>0.2516174890372561</v>
+        <v>0.09459929947370169</v>
       </c>
       <c r="AD3">
-        <v>44.3</v>
+        <v>45.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>44.3</v>
+        <v>45.6</v>
       </c>
       <c r="AG3">
-        <v>16.5</v>
+        <v>14.3</v>
       </c>
       <c r="AH3">
-        <v>0.09968496849684967</v>
+        <v>0.1526104417670683</v>
       </c>
       <c r="AI3">
-        <v>0.1951541850220264</v>
+        <v>0.1987794245858762</v>
       </c>
       <c r="AJ3">
-        <v>0.03960633701392222</v>
+        <v>0.05345794392523365</v>
       </c>
       <c r="AK3">
-        <v>0.08283132530120481</v>
+        <v>0.07218576476527006</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AM3">
-        <v>-1.11</v>
+        <v>1.37</v>
       </c>
       <c r="AN3">
-        <v>0.6161335187760778</v>
+        <v>0.8752399232245681</v>
+      </c>
+      <c r="AO3">
+        <v>34.8905109489051</v>
       </c>
       <c r="AP3">
-        <v>0.2294853963838664</v>
+        <v>0.2744721689059501</v>
       </c>
       <c r="AQ3">
-        <v>-61.35135135135134</v>
+        <v>34.8905109489051</v>
       </c>
     </row>
     <row r="4">
@@ -853,10 +856,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0992</v>
+        <v>0.0307</v>
       </c>
       <c r="E4">
-        <v>0.311</v>
+        <v>0.0733</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -871,28 +874,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>25.5</v>
+        <v>24</v>
       </c>
       <c r="L4">
-        <v>0.8415841584158416</v>
+        <v>0.9486166007905138</v>
       </c>
       <c r="M4">
-        <v>27.9</v>
+        <v>28.8</v>
       </c>
       <c r="N4">
-        <v>0.08746081504702194</v>
+        <v>0.1465648854961832</v>
       </c>
       <c r="O4">
-        <v>1.094117647058823</v>
+        <v>1.2</v>
       </c>
       <c r="P4">
-        <v>27.9</v>
+        <v>28.8</v>
       </c>
       <c r="Q4">
-        <v>0.08746081504702194</v>
+        <v>0.1465648854961832</v>
       </c>
       <c r="R4">
-        <v>1.094117647058823</v>
+        <v>1.2</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -901,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.968</v>
+        <v>0.793</v>
       </c>
       <c r="V4">
-        <v>0.00303448275862069</v>
+        <v>0.004035623409669211</v>
       </c>
       <c r="W4">
-        <v>0.3935185185185185</v>
+        <v>0.3582089552238806</v>
       </c>
       <c r="X4">
-        <v>0.03642434289743676</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="Y4">
-        <v>0.3570941756210818</v>
+        <v>0.2868627190456676</v>
       </c>
       <c r="Z4">
-        <v>0.5003137280803144</v>
+        <v>0.3831475648170584</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.03642434289743676</v>
+        <v>0.07134623617821302</v>
       </c>
       <c r="AC4">
-        <v>-0.03642434289743676</v>
+        <v>-0.07134623617821302</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -937,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.968</v>
+        <v>-0.793</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -946,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.003043718871057001</v>
+        <v>-0.00405197565748798</v>
       </c>
       <c r="AK4">
-        <v>-0.01463739188290087</v>
+        <v>-0.01418427030604397</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -975,10 +978,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.164</v>
+        <v>-0.0383</v>
       </c>
       <c r="E5">
-        <v>0.123</v>
+        <v>-0.099</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -993,28 +996,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>14.7</v>
+        <v>7.38</v>
       </c>
       <c r="L5">
-        <v>0.3909574468085106</v>
+        <v>0.3863874345549738</v>
       </c>
       <c r="M5">
-        <v>15.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N5">
-        <v>0.1763341067285383</v>
+        <v>0.2037470725995316</v>
       </c>
       <c r="O5">
-        <v>1.034013605442177</v>
+        <v>1.178861788617886</v>
       </c>
       <c r="P5">
-        <v>15.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Q5">
-        <v>0.1763341067285383</v>
+        <v>0.2037470725995316</v>
       </c>
       <c r="R5">
-        <v>1.034013605442177</v>
+        <v>1.178861788617886</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,174 +1026,64 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>37.9</v>
+        <v>22.9</v>
       </c>
       <c r="V5">
-        <v>0.4396751740139211</v>
+        <v>0.5362997658079625</v>
       </c>
       <c r="W5">
-        <v>0.3585365853658536</v>
+        <v>0.1708333333333333</v>
       </c>
       <c r="X5">
-        <v>0.03666625791970362</v>
+        <v>0.07191083334417672</v>
       </c>
       <c r="Y5">
-        <v>0.32187032744615</v>
+        <v>0.09892249998915659</v>
       </c>
       <c r="Z5">
-        <v>5.71428571428571</v>
+        <v>2.907153729071534</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.03646183446967928</v>
+        <v>0.07147037530836373</v>
       </c>
       <c r="AC5">
-        <v>-0.03646183446967928</v>
+        <v>-0.07147037530836373</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>0.962</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.27</v>
+        <v>0.962</v>
       </c>
       <c r="AG5">
-        <v>-36.63</v>
+        <v>-21.938</v>
       </c>
       <c r="AH5">
-        <v>0.0145192637475706</v>
+        <v>0.02203288901103934</v>
       </c>
       <c r="AI5">
-        <v>0.02855857881718012</v>
+        <v>0.02431626308073404</v>
       </c>
       <c r="AJ5">
-        <v>-0.7389550131127696</v>
+        <v>-1.05664194200944</v>
       </c>
       <c r="AK5">
-        <v>-5.575342465753418</v>
+        <v>-1.316648661625255</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.423</v>
+        <v>-0.398</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Israel</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Electreon Wireless Ltd (TASE:ELWS)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brokerage &amp; Investment Banking</t>
-        </is>
-      </c>
-      <c r="K6">
-        <v>-14</v>
-      </c>
-      <c r="M6">
-        <v>-0</v>
-      </c>
-      <c r="N6">
-        <v>-0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>-0</v>
-      </c>
-      <c r="Q6">
-        <v>-0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="U6">
-        <v>1.18</v>
-      </c>
-      <c r="V6">
-        <v>0.001838578996572141</v>
-      </c>
-      <c r="W6">
-        <v>-0.2766798418972332</v>
-      </c>
-      <c r="X6">
-        <v>0.03647167310382099</v>
-      </c>
-      <c r="Y6">
-        <v>-0.3131515150010542</v>
-      </c>
-      <c r="Z6">
-        <v>0</v>
-      </c>
-      <c r="AA6">
-        <v>-0.3163136634679091</v>
-      </c>
-      <c r="AB6">
-        <v>0.03644198470590923</v>
-      </c>
-      <c r="AC6">
-        <v>-0.3527556481738183</v>
-      </c>
-      <c r="AD6">
-        <v>1.85</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>1.85</v>
-      </c>
-      <c r="AG6">
-        <v>0.6700000000000002</v>
-      </c>
-      <c r="AH6">
-        <v>0.002874232890546104</v>
-      </c>
-      <c r="AI6">
-        <v>0.03858185610010428</v>
-      </c>
-      <c r="AJ6">
-        <v>0.001042850249817112</v>
-      </c>
-      <c r="AK6">
-        <v>0.01432542227923883</v>
-      </c>
-      <c r="AL6">
-        <v>0.007</v>
-      </c>
-      <c r="AM6">
-        <v>-0.728</v>
-      </c>
-      <c r="AN6">
-        <v>-0.1275862068965517</v>
-      </c>
-      <c r="AO6">
-        <v>-2114.285714285714</v>
-      </c>
-      <c r="AP6">
-        <v>-0.04620689655172415</v>
-      </c>
-      <c r="AQ6">
-        <v>20.32967032967033</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/israel/israel_brokerage_investment_banking.xlsx
+++ b/research/traditional_assets/database/data/israel/israel_brokerage_investment_banking.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0307</v>
+        <v>-0.0202</v>
       </c>
       <c r="E2">
-        <v>0.0733</v>
+        <v>0.00668</v>
       </c>
       <c r="G2">
-        <v>0.3328735632183908</v>
+        <v>0.2497581721147432</v>
       </c>
       <c r="H2">
-        <v>0.3328735632183908</v>
+        <v>0.2489159439626418</v>
       </c>
       <c r="I2">
-        <v>0.2197701149425287</v>
+        <v>0.3202134756504336</v>
       </c>
       <c r="J2">
-        <v>0.1771868571465101</v>
+        <v>0.2703883443951661</v>
       </c>
       <c r="K2">
-        <v>52.68</v>
+        <v>65.89</v>
       </c>
       <c r="L2">
-        <v>0.2422068965517241</v>
+        <v>0.2747248165443629</v>
       </c>
       <c r="M2">
-        <v>47.7</v>
+        <v>49.29</v>
       </c>
       <c r="N2">
-        <v>0.09687246141348498</v>
+        <v>0.08061825318940137</v>
       </c>
       <c r="O2">
-        <v>0.9054669703872438</v>
+        <v>0.748064956746092</v>
       </c>
       <c r="P2">
-        <v>47.7</v>
+        <v>49.29</v>
       </c>
       <c r="Q2">
-        <v>0.09687246141348498</v>
+        <v>0.08061825318940137</v>
       </c>
       <c r="R2">
-        <v>0.9054669703872438</v>
+        <v>0.748064956746092</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>54.993</v>
+        <v>49.247</v>
       </c>
       <c r="V2">
-        <v>0.1116835905767669</v>
+        <v>0.08054792280013084</v>
       </c>
       <c r="W2">
-        <v>0.1708333333333333</v>
+        <v>0.2576722640416908</v>
       </c>
       <c r="X2">
-        <v>0.07191083334417672</v>
+        <v>0.06079928407813033</v>
       </c>
       <c r="Y2">
-        <v>0.09892249998915659</v>
+        <v>0.1968729799635605</v>
       </c>
       <c r="Z2">
-        <v>0.8247946545722065</v>
+        <v>0.9243493442376545</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.07134623617821302</v>
+        <v>0.06063976395014439</v>
       </c>
       <c r="AC2">
-        <v>-0.07134623617821302</v>
+        <v>-0.06060108164794122</v>
       </c>
       <c r="AD2">
-        <v>46.562</v>
+        <v>55.673</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>46.562</v>
+        <v>55.673</v>
       </c>
       <c r="AG2">
-        <v>-8.430999999999997</v>
+        <v>6.426000000000002</v>
       </c>
       <c r="AH2">
-        <v>0.0863919905299446</v>
+        <v>0.08345863196381806</v>
       </c>
       <c r="AI2">
-        <v>0.1429764602563394</v>
+        <v>0.1619941048613071</v>
       </c>
       <c r="AJ2">
-        <v>-0.01742053726581661</v>
+        <v>0.01040098668557167</v>
       </c>
       <c r="AK2">
-        <v>-0.0311487462546505</v>
+        <v>0.02182551812679587</v>
       </c>
       <c r="AL2">
-        <v>1.37</v>
+        <v>0.713</v>
       </c>
       <c r="AM2">
-        <v>0.9720000000000001</v>
+        <v>-0.497</v>
       </c>
       <c r="AN2">
-        <v>0.8937044145873321</v>
+        <v>0.6814320685434516</v>
       </c>
       <c r="AO2">
-        <v>34.8905109489051</v>
+        <v>107.7138849929874</v>
       </c>
       <c r="AP2">
-        <v>-0.1618234165067178</v>
+        <v>0.07865361077111385</v>
       </c>
       <c r="AQ2">
-        <v>49.17695473251028</v>
+        <v>-154.5271629778672</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>I.B.I Investment House Ltd. (TASE:IBI)</t>
+          <t>I.B.I. Investment House Ltd (TASE:IBI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.161</v>
+        <v>0.175</v>
       </c>
       <c r="E3">
-        <v>0.115</v>
+        <v>0.217</v>
       </c>
       <c r="G3">
-        <v>0.4182553437319469</v>
+        <v>0.2816267042783263</v>
       </c>
       <c r="H3">
-        <v>0.4182553437319469</v>
+        <v>0.2806770098730607</v>
       </c>
       <c r="I3">
-        <v>0.2761409589832467</v>
+        <v>0.3610719322990127</v>
       </c>
       <c r="J3">
-        <v>0.1826589416882501</v>
+        <v>0.2655938508722939</v>
       </c>
       <c r="K3">
-        <v>21.3</v>
+        <v>44.5</v>
       </c>
       <c r="L3">
-        <v>0.123050259965338</v>
+        <v>0.2092148566055477</v>
       </c>
       <c r="M3">
-        <v>10.2</v>
+        <v>29.6</v>
       </c>
       <c r="N3">
-        <v>0.04028436018957346</v>
+        <v>0.08870242732993708</v>
       </c>
       <c r="O3">
-        <v>0.4788732394366197</v>
+        <v>0.6651685393258427</v>
       </c>
       <c r="P3">
-        <v>10.2</v>
+        <v>29.6</v>
       </c>
       <c r="Q3">
-        <v>0.04028436018957346</v>
+        <v>0.08870242732993708</v>
       </c>
       <c r="R3">
-        <v>0.4788732394366197</v>
+        <v>0.6651685393258427</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>31.3</v>
+        <v>23.4</v>
       </c>
       <c r="V3">
-        <v>0.1236176935229068</v>
+        <v>0.07012286484866646</v>
       </c>
       <c r="W3">
-        <v>0.1219931271477663</v>
+        <v>0.2576722640416908</v>
       </c>
       <c r="X3">
-        <v>0.07585951992501166</v>
+        <v>0.06336786560895503</v>
       </c>
       <c r="Y3">
-        <v>0.04613360722275467</v>
+        <v>0.1943043984327358</v>
       </c>
       <c r="Z3">
-        <v>0.9058084772370488</v>
+        <v>1.137433155080214</v>
       </c>
       <c r="AA3">
-        <v>0.1654540178243646</v>
+        <v>0.3020952517675771</v>
       </c>
       <c r="AB3">
-        <v>0.07085471835066295</v>
+        <v>0.06077933500923501</v>
       </c>
       <c r="AC3">
-        <v>0.09459929947370169</v>
+        <v>0.2413159167583421</v>
       </c>
       <c r="AD3">
-        <v>45.6</v>
+        <v>55</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>45.6</v>
+        <v>55</v>
       </c>
       <c r="AG3">
-        <v>14.3</v>
+        <v>31.6</v>
       </c>
       <c r="AH3">
-        <v>0.1526104417670683</v>
+        <v>0.1414972986879341</v>
       </c>
       <c r="AI3">
-        <v>0.1987794245858762</v>
+        <v>0.2250409165302782</v>
       </c>
       <c r="AJ3">
-        <v>0.05345794392523365</v>
+        <v>0.08650424308787298</v>
       </c>
       <c r="AK3">
-        <v>0.07218576476527006</v>
+        <v>0.1429864253393665</v>
       </c>
       <c r="AL3">
-        <v>1.37</v>
+        <v>0.713</v>
       </c>
       <c r="AM3">
-        <v>1.37</v>
+        <v>0.713</v>
       </c>
       <c r="AN3">
-        <v>0.8752399232245681</v>
+        <v>0.6731946144430845</v>
       </c>
       <c r="AO3">
-        <v>34.8905109489051</v>
+        <v>107.7138849929874</v>
       </c>
       <c r="AP3">
-        <v>0.2744721689059501</v>
+        <v>0.386780905752754</v>
       </c>
       <c r="AQ3">
-        <v>34.8905109489051</v>
+        <v>107.7138849929874</v>
       </c>
     </row>
     <row r="4">
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0307</v>
+        <v>-0.0202</v>
       </c>
       <c r="E4">
-        <v>0.0733</v>
+        <v>0.00668</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -874,28 +874,28 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>24</v>
+        <v>19.7</v>
       </c>
       <c r="L4">
-        <v>0.9486166007905138</v>
+        <v>0.9471153846153846</v>
       </c>
       <c r="M4">
-        <v>28.8</v>
+        <v>17.7</v>
       </c>
       <c r="N4">
-        <v>0.1465648854961832</v>
+        <v>0.08019936565473494</v>
       </c>
       <c r="O4">
-        <v>1.2</v>
+        <v>0.8984771573604061</v>
       </c>
       <c r="P4">
-        <v>28.8</v>
+        <v>17.7</v>
       </c>
       <c r="Q4">
-        <v>0.1465648854961832</v>
+        <v>0.08019936565473494</v>
       </c>
       <c r="R4">
-        <v>1.2</v>
+        <v>0.8984771573604061</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -904,31 +904,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.793</v>
+        <v>0.647</v>
       </c>
       <c r="V4">
-        <v>0.004035623409669211</v>
+        <v>0.002931581332125057</v>
       </c>
       <c r="W4">
-        <v>0.3582089552238806</v>
+        <v>0.3480565371024735</v>
       </c>
       <c r="X4">
-        <v>0.07134623617821302</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="Y4">
-        <v>0.2868627190456676</v>
+        <v>0.2874554554545323</v>
       </c>
       <c r="Z4">
-        <v>0.3831475648170584</v>
+        <v>0.3727131005071048</v>
       </c>
       <c r="AA4">
         <v>0</v>
       </c>
       <c r="AB4">
-        <v>0.07134623617821302</v>
+        <v>0.06060108164794122</v>
       </c>
       <c r="AC4">
-        <v>-0.07134623617821302</v>
+        <v>-0.06060108164794122</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -940,7 +940,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-0.793</v>
+        <v>-0.647</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -949,10 +949,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.00405197565748798</v>
+        <v>-0.002940200769814545</v>
       </c>
       <c r="AK4">
-        <v>-0.01418427030604397</v>
+        <v>-0.01190366677092341</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Poalim I.B.I.-Managing &amp; Underwriting Ltd (TASE:PIU)</t>
+          <t>I.B.I.- Managing &amp; Underwriting Ltd (TASE:IBIU)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -978,10 +978,10 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0383</v>
+        <v>-0.158</v>
       </c>
       <c r="E5">
-        <v>-0.099</v>
+        <v>-0.248</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -996,28 +996,28 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>7.38</v>
+        <v>1.69</v>
       </c>
       <c r="L5">
-        <v>0.3863874345549738</v>
+        <v>0.2665615141955836</v>
       </c>
       <c r="M5">
-        <v>8.699999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="N5">
-        <v>0.2037470725995316</v>
+        <v>0.03491228070175439</v>
       </c>
       <c r="O5">
-        <v>1.178861788617886</v>
+        <v>1.177514792899408</v>
       </c>
       <c r="P5">
-        <v>8.699999999999999</v>
+        <v>1.99</v>
       </c>
       <c r="Q5">
-        <v>0.2037470725995316</v>
+        <v>0.03491228070175439</v>
       </c>
       <c r="R5">
-        <v>1.178861788617886</v>
+        <v>1.177514792899408</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1026,61 +1026,61 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>22.9</v>
+        <v>25.2</v>
       </c>
       <c r="V5">
-        <v>0.5362997658079625</v>
+        <v>0.4421052631578947</v>
       </c>
       <c r="W5">
-        <v>0.1708333333333333</v>
+        <v>0.04378238341968912</v>
       </c>
       <c r="X5">
-        <v>0.07191083334417672</v>
+        <v>0.06079928407813033</v>
       </c>
       <c r="Y5">
-        <v>0.09892249998915659</v>
+        <v>-0.01701690065844121</v>
       </c>
       <c r="Z5">
-        <v>2.907153729071534</v>
+        <v>0.3805065418317127</v>
       </c>
       <c r="AA5">
         <v>0</v>
       </c>
       <c r="AB5">
-        <v>0.07147037530836373</v>
+        <v>0.06063976395014439</v>
       </c>
       <c r="AC5">
-        <v>-0.07147037530836373</v>
+        <v>-0.06063976395014439</v>
       </c>
       <c r="AD5">
-        <v>0.962</v>
+        <v>0.673</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.962</v>
+        <v>0.673</v>
       </c>
       <c r="AG5">
-        <v>-21.938</v>
+        <v>-24.527</v>
       </c>
       <c r="AH5">
-        <v>0.02203288901103934</v>
+        <v>0.01166923863853103</v>
       </c>
       <c r="AI5">
-        <v>0.02431626308073404</v>
+        <v>0.01520113839134461</v>
       </c>
       <c r="AJ5">
-        <v>-1.05664194200944</v>
+        <v>-0.7553044067379054</v>
       </c>
       <c r="AK5">
-        <v>-1.316648661625255</v>
+        <v>-1.285953966339852</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-0.398</v>
+        <v>-1.21</v>
       </c>
       <c r="AQ5">
         <v>-0</v>
